--- a/output/upload/S00026_1230_장애인전용_곰두리보장보험_무배당.xlsx
+++ b/output/upload/S00026_1230_장애인전용_곰두리보장보험_무배당.xlsx
@@ -1304,17 +1304,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -1394,17 +1386,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
@@ -1484,17 +1468,9 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
@@ -1574,17 +1550,9 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="inlineStr">
@@ -1664,17 +1632,9 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="inlineStr">
@@ -1754,17 +1714,9 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
@@ -1844,17 +1796,9 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
@@ -1934,17 +1878,9 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="6" t="inlineStr">
@@ -2024,17 +1960,9 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="6" t="inlineStr">
@@ -2114,17 +2042,9 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="6" t="inlineStr">
@@ -2204,17 +2124,9 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="6" t="inlineStr">
@@ -2294,17 +2206,9 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="6" t="inlineStr">
@@ -2384,17 +2288,9 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="6" t="inlineStr">
@@ -2474,17 +2370,9 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="6" t="inlineStr">
@@ -2564,17 +2452,9 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="6" t="inlineStr">
@@ -2654,17 +2534,9 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="6" t="inlineStr">

--- a/output/upload/S00026_1230_장애인전용_곰두리보장보험_무배당.xlsx
+++ b/output/upload/S00026_1230_장애인전용_곰두리보장보험_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1386,11 +1406,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1468,11 +1508,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1550,11 +1610,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1632,11 +1712,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1714,11 +1814,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1796,11 +1916,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1878,11 +2018,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1960,11 +2120,31 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2042,11 +2222,31 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2124,11 +2324,31 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2206,11 +2426,31 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2288,11 +2528,31 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2370,11 +2630,31 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2452,11 +2732,31 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2534,11 +2834,31 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00026_1230_장애인전용_곰두리보장보험_무배당.xlsx
+++ b/output/upload/S00026_1230_장애인전용_곰두리보장보험_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/output/upload/S00026_1230_장애인전용_곰두리보장보험_무배당.xlsx
+++ b/output/upload/S00026_1230_장애인전용_곰두리보장보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1339,7 +1339,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J7" s="6" t="n">
         <v>15</v>
       </c>
@@ -1441,7 +1445,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J8" s="6" t="n">
         <v>15</v>
       </c>
@@ -1543,7 +1551,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J9" s="6" t="n">
         <v>15</v>
       </c>
@@ -1645,7 +1657,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J10" s="6" t="n">
         <v>15</v>
       </c>
@@ -1747,7 +1763,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I11" s="6" t="n"/>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J11" s="6" t="n">
         <v>15</v>
       </c>
@@ -1849,7 +1869,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I12" s="6" t="n"/>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J12" s="6" t="n">
         <v>15</v>
       </c>
@@ -1951,7 +1975,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I13" s="6" t="n"/>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J13" s="6" t="n">
         <v>15</v>
       </c>
@@ -2053,7 +2081,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I14" s="6" t="n"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J14" s="6" t="n">
         <v>15</v>
       </c>
@@ -2155,7 +2187,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I15" s="6" t="n"/>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J15" s="6" t="n">
         <v>15</v>
       </c>
@@ -2257,7 +2293,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I16" s="6" t="n"/>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J16" s="6" t="n">
         <v>15</v>
       </c>
@@ -2359,7 +2399,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I17" s="6" t="n"/>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J17" s="6" t="n">
         <v>15</v>
       </c>
@@ -2461,7 +2505,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I18" s="6" t="n"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J18" s="6" t="n">
         <v>15</v>
       </c>
@@ -2563,7 +2611,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I19" s="6" t="n"/>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J19" s="6" t="n">
         <v>15</v>
       </c>
@@ -2665,7 +2717,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I20" s="6" t="n"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J20" s="6" t="n">
         <v>15</v>
       </c>
@@ -2767,7 +2823,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I21" s="6" t="n"/>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J21" s="6" t="n">
         <v>15</v>
       </c>
@@ -2869,7 +2929,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I22" s="6" t="n"/>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J22" s="6" t="n">
         <v>15</v>
       </c>
